--- a/Design/修女.xlsx
+++ b/Design/修女.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13460" windowHeight="11630"/>
+    <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
     <t>生命护符</t>
   </si>
   <si>
-    <t>每过3回合，回复5生命</t>
+    <t>每过3回合，回复3生命</t>
   </si>
   <si>
     <t>画像</t>
@@ -465,7 +465,7 @@
     <t>呵斥</t>
   </si>
   <si>
-    <t>造成卡组内祷告牌数量的伤害</t>
+    <t>造成抽牌堆、弃牌堆、手牌、消耗堆中祷告牌数量的伤害</t>
   </si>
   <si>
     <t>数量+3的伤害</t>
@@ -567,7 +567,7 @@
     <t>重生祈祷</t>
   </si>
   <si>
-    <t>祷告2：将随机3张祷告牌置入祈祷区</t>
+    <t>祷告2：将随机3张祷告牌置入祈祷区(不允许生成生命祷告)</t>
   </si>
   <si>
     <t>4张</t>
